--- a/IEEE_Conference_Template/results_surrogate/data/experiment_results.xlsx
+++ b/IEEE_Conference_Template/results_surrogate/data/experiment_results.xlsx
@@ -778,12 +778,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>±2.1</t>
+          <t>±2.4</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>
@@ -1058,16 +1058,16 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>7</v>
-      </c>
       <c r="K5" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>29</v>
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>3</v>
@@ -1199,10 +1199,10 @@
         <v>6</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>51</v>
@@ -1237,16 +1237,16 @@
         <v>30</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -1395,11 +1395,11 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>51</v>
@@ -1410,19 +1410,19 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -1724,13 +1724,13 @@
         <v>7</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>3</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
@@ -1747,11 +1747,11 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>51</v>
@@ -1762,19 +1762,19 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>5</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>resource.zone in {'level2_supervisory', 'level1_control'}</t>
+          <t>resource.zone in {'level1_control', 'level2_supervisory'}</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>resource.zone in {'level2_supervisory', 'level1_control', 'level0_field'}
+          <t>resource.zone in {'level0_field', 'level1_control', 'level2_supervisory'}
 environment.plant_mode neq emergency</t>
         </is>
       </c>
